--- a/data/trans_orig/IP3103-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3103-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34493</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44827</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57127</t>
+          <t>56749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38786</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56667</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32659</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37832</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>58834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115427</t>
+          <t>114259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141177</t>
+          <t>140417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106156</t>
+          <t>105337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131796</t>
+          <t>130736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227153</t>
+          <t>228369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>263317</t>
+          <t>265013</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>78115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102364</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88247</t>
+          <t>89072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113144</t>
+          <t>114106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173951</t>
+          <t>171258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210647</t>
+          <t>207707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51679</t>
+          <t>50974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>68612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>66933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84854</t>
+          <t>84981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>122579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149029</t>
+          <t>148240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38318</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78082</t>
+          <t>78455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103032</t>
+          <t>102113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23474</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>74551</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97748</t>
+          <t>97259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113274</t>
+          <t>112496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>171740</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202694</t>
+          <t>200929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96497</t>
+          <t>97855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66766</t>
+          <t>66110</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146017</t>
+          <t>147667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177311</t>
+          <t>177410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,82 +3588,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>60773</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>50314</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>74011</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>124941</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>108587</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>143025</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>8,28%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>60773</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>49029</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>72859</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>124941</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>108712</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>144281</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>281962</t>
+          <t>282065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>323639</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>311377</t>
+          <t>313409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>354940</t>
+          <t>356244</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>604329</t>
+          <t>606171</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>664654</t>
+          <t>665452</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>222073</t>
+          <t>221236</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>261997</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>226317</t>
+          <t>227530</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>267321</t>
+          <t>266189</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>463488</t>
+          <t>461574</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>522266</t>
+          <t>516325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65608</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44146</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>57131</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>79259</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>32810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51154</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44550</t>
+          <t>43117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>80046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92005</t>
+          <t>92237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115997</t>
+          <t>117407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121873</t>
+          <t>121355</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148378</t>
+          <t>148879</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222552</t>
+          <t>221201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261637</t>
+          <t>258668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58443</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>80569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86755</t>
+          <t>86698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129423</t>
+          <t>129020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164540</t>
+          <t>162952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29157</t>
+          <t>29308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59831</t>
+          <t>59916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>72047</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>92560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57822</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78240</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135956</t>
+          <t>135888</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164605</t>
+          <t>166282</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49107</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54464</t>
+          <t>53528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71138</t>
+          <t>70958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96681</t>
+          <t>97062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40324</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>44961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68141</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71218</t>
+          <t>70414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>92328</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61668</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>82577</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>137805</t>
+          <t>137908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>167356</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38436</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56849</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>50480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69096</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93461</t>
+          <t>94396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121286</t>
+          <t>121941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>20231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>114339</t>
+          <t>115132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92404</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122894</t>
+          <t>123881</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>184273</t>
+          <t>184710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>228155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>282638</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>324864</t>
+          <t>323176</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>286857</t>
+          <t>285578</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>329726</t>
+          <t>330491</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>580151</t>
+          <t>584463</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>641218</t>
+          <t>643905</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>162222</t>
+          <t>160986</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>200140</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>178985</t>
+          <t>175618</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>217557</t>
+          <t>215916</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>350091</t>
+          <t>351629</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>404820</t>
+          <t>406204</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>55659</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>80212</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>62312</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>125655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>160081</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>31176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40744</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>32519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47745</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66783</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35196</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>55502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>85684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>112120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>147879</t>
+          <t>145169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>181249</t>
+          <t>179762</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56227</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>78083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>60630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85751</t>
+          <t>86037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125222</t>
+          <t>124611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156852</t>
+          <t>157021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45640</t>
+          <t>44704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65836</t>
+          <t>64484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>69929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98117</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>128108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>32727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59809</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64127</t>
+          <t>64368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>86093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57329</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>80094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127362</t>
+          <t>128413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159394</t>
+          <t>160123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>38977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58790</t>
+          <t>59238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79503</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109641</t>
+          <t>107705</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>49750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54778</t>
+          <t>55357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97973</t>
+          <t>100185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66512</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89087</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67845</t>
+          <t>67934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120520</t>
+          <t>120407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150892</t>
+          <t>150146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53395</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56701</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>75377</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102766</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27396</t>
+          <t>27349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44591</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>40580</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>60135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>71529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97617</t>
+          <t>97792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61481</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>88853</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128712</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166873</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223376</t>
+          <t>221770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>264388</t>
+          <t>263654</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>228659</t>
+          <t>228204</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>271364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>464806</t>
+          <t>464451</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>522829</t>
+          <t>523166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>154788</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>193295</t>
+          <t>194104</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>172585</t>
+          <t>173055</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>211685</t>
+          <t>209678</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>338515</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>393568</t>
+          <t>393357</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>143423</t>
+          <t>142833</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178662</t>
+          <t>178026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>161860</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>198444</t>
+          <t>199892</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>313279</t>
+          <t>315970</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>365024</t>
+          <t>367613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
